--- a/HW4/result/HW4.xlsx
+++ b/HW4/result/HW4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nuna\Documents\GitHub\DADS7102\HW4\result\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\T00229\Documents\GitHub\DADS7102\HW4\result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A0BC3CA-6C16-47C3-8E9D-D48D7234A5CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D01EDF7-7DA0-4F4B-A80A-750284FE0867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{34DA60CE-96CD-40DE-89EC-63BE59E8EFBC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{34DA60CE-96CD-40DE-89EC-63BE59E8EFBC}"/>
   </bookViews>
   <sheets>
     <sheet name="FixedCost" sheetId="1" r:id="rId1"/>
@@ -109,7 +109,7 @@
     <definedName name="solver_nwt" localSheetId="2" hidden="1">1</definedName>
     <definedName name="solver_opt" localSheetId="1" hidden="1">CapitalBudget!$B$17</definedName>
     <definedName name="solver_opt" localSheetId="0" hidden="1">FixedCost!$B$30</definedName>
-    <definedName name="solver_opt" localSheetId="2" hidden="1">ProdPlanning!$H$36</definedName>
+    <definedName name="solver_opt" localSheetId="2" hidden="1">ProdPlanning!$Y$8</definedName>
     <definedName name="solver_pre" localSheetId="1" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="0" hidden="1">0.000001</definedName>
     <definedName name="solver_pre" localSheetId="2" hidden="1">0.000001</definedName>
@@ -776,9 +776,12 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
+      <sheetName val="Advertising "/>
+      <sheetName val="Advertising _Sensitivity Report"/>
+      <sheetName val="monopolist"/>
       <sheetName val="Sensitivity Report 1"/>
       <sheetName val="ProductMix"/>
       <sheetName val="ProductMix_add_on"/>
@@ -807,6 +810,7 @@
       <sheetName val="MMULT"/>
       <sheetName val="MDETERM"/>
       <sheetName val="Peakload"/>
+      <sheetName val="GameTheory"/>
       <sheetName val="Portfolio"/>
       <sheetName val="EOQ"/>
       <sheetName val="SVM1"/>
@@ -822,8 +826,11 @@
       <sheetData sheetId="4" refreshError="1"/>
       <sheetData sheetId="5" refreshError="1"/>
       <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8">
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11">
         <row r="6">
           <cell r="K6">
             <v>2</v>
@@ -895,9 +902,6 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
       <sheetData sheetId="12" refreshError="1"/>
       <sheetData sheetId="13" refreshError="1"/>
       <sheetData sheetId="14" refreshError="1"/>
@@ -906,7 +910,10 @@
       <sheetData sheetId="17" refreshError="1"/>
       <sheetData sheetId="18" refreshError="1"/>
       <sheetData sheetId="19" refreshError="1"/>
-      <sheetData sheetId="20">
+      <sheetData sheetId="20" refreshError="1"/>
+      <sheetData sheetId="21" refreshError="1"/>
+      <sheetData sheetId="22" refreshError="1"/>
+      <sheetData sheetId="23">
         <row r="10">
           <cell r="B10">
             <v>0</v>
@@ -931,9 +938,6 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="21" refreshError="1"/>
-      <sheetData sheetId="22" refreshError="1"/>
-      <sheetData sheetId="23" refreshError="1"/>
       <sheetData sheetId="24" refreshError="1"/>
       <sheetData sheetId="25" refreshError="1"/>
       <sheetData sheetId="26" refreshError="1"/>
@@ -944,17 +948,18 @@
       <sheetData sheetId="31" refreshError="1"/>
       <sheetData sheetId="32" refreshError="1"/>
       <sheetData sheetId="33" refreshError="1"/>
+      <sheetData sheetId="34" refreshError="1"/>
+      <sheetData sheetId="35" refreshError="1"/>
+      <sheetData sheetId="36" refreshError="1"/>
+      <sheetData sheetId="37" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sensitivity Report 1"/>
       <sheetName val="ProductMix"/>
